--- a/GameConfig/Datas/模型/角色模型配对表.xlsx
+++ b/GameConfig/Datas/模型/角色模型配对表.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\GitHub_Project\DGame_Fantasy\GameConfig\Datas\模型\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{F9080461-B0ED-49C7-AC1D-2B6C7135AD25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="1"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="角色模型配对表" sheetId="6" r:id="rId1"/>
@@ -12,6 +18,7 @@
     <sheet name="（已废弃）角色模型配对表" sheetId="7" state="hidden" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -29,18 +36,19 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>wzd</author>
     <author>asus</author>
   </authors>
   <commentList>
-    <comment ref="B4" authorId="0">
+    <comment ref="B4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>1 - 体形男
@@ -48,14 +56,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="D4" authorId="1">
+    <comment ref="D4" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>asus:</t>
         </r>
@@ -63,7 +71,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -72,6 +80,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>确认的</t>
@@ -80,7 +89,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>ID</t>
         </r>
@@ -88,6 +97,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>置黑，代图置红
@@ -98,7 +108,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>--</t>
         </r>
@@ -106,6 +116,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>男单数，女双数</t>
@@ -117,18 +128,19 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>wzd</author>
     <author>asus</author>
   </authors>
   <commentList>
-    <comment ref="B4" authorId="0">
+    <comment ref="B4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>1 - 体形男
@@ -136,14 +148,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="D4" authorId="1">
+    <comment ref="D4" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>asus:</t>
         </r>
@@ -151,7 +163,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -160,6 +172,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>确认的</t>
@@ -168,7 +181,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>ID</t>
         </r>
@@ -176,6 +189,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>置黑，代图置红
@@ -186,7 +200,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>--</t>
         </r>
@@ -194,6 +208,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>男单数，女双数</t>
@@ -205,18 +220,19 @@
 </file>
 
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>wzd</author>
     <author>asus</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>1 - 体形男
@@ -224,14 +240,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="1">
+    <comment ref="C1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>asus:</t>
         </r>
@@ -239,7 +255,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -248,6 +264,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>确认的</t>
@@ -256,7 +273,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>ID</t>
         </r>
@@ -264,6 +281,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>置黑，代图置红
@@ -274,7 +292,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>--</t>
         </r>
@@ -282,20 +300,21 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>男单数，女双数</t>
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="1">
+    <comment ref="E1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000003000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>asus:</t>
         </r>
@@ -303,7 +322,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -312,6 +331,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>验错，</t>
@@ -320,7 +340,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>ID</t>
         </r>
@@ -328,6 +348,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">不存在将单元格置红
@@ -648,14 +669,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="29">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -667,6 +682,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -674,17 +690,20 @@
       <sz val="10"/>
       <color theme="0"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -692,6 +711,7 @@
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -699,170 +719,51 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -883,7 +784,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.149906918546098"/>
+        <fgColor theme="0" tint="-0.1498764000366222"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -901,186 +802,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399853511154515"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.39982299264503923"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -1090,16 +823,16 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="0" tint="-0.149784844508194"/>
+        <color theme="0" tint="-0.14975432599871821"/>
       </left>
       <right style="thin">
-        <color theme="0" tint="-0.149784844508194"/>
+        <color theme="0" tint="-0.14975432599871821"/>
       </right>
       <top style="thin">
-        <color theme="0" tint="-0.149784844508194"/>
+        <color theme="0" tint="-0.14975432599871821"/>
       </top>
       <bottom style="thin">
-        <color theme="0" tint="-0.149784844508194"/>
+        <color theme="0" tint="-0.14975432599871821"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1107,7 +840,7 @@
       <left/>
       <right/>
       <top style="thin">
-        <color theme="0" tint="-0.149784844508194"/>
+        <color theme="0" tint="-0.14975432599871821"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -1115,10 +848,10 @@
     <border>
       <left/>
       <right style="thin">
-        <color theme="0" tint="-0.149784844508194"/>
+        <color theme="0" tint="-0.14975432599871821"/>
       </right>
       <top style="thin">
-        <color theme="0" tint="-0.149784844508194"/>
+        <color theme="0" tint="-0.14975432599871821"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -1126,7 +859,7 @@
     <border>
       <left/>
       <right style="thin">
-        <color theme="0" tint="-0.149784844508194"/>
+        <color theme="0" tint="-0.14975432599871821"/>
       </right>
       <top/>
       <bottom/>
@@ -1134,13 +867,13 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="0" tint="-0.149784844508194"/>
+        <color theme="0" tint="-0.14975432599871821"/>
       </left>
       <right style="thin">
-        <color theme="0" tint="-0.149784844508194"/>
+        <color theme="0" tint="-0.14975432599871821"/>
       </right>
       <top style="thin">
-        <color theme="0" tint="-0.149784844508194"/>
+        <color theme="0" tint="-0.14975432599871821"/>
       </top>
       <bottom style="thin">
         <color auto="1"/>
@@ -1164,277 +897,41 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="0" tint="-0.149784844508194"/>
+        <color theme="0" tint="-0.14975432599871821"/>
       </left>
       <right style="thin">
-        <color theme="0" tint="-0.149784844508194"/>
+        <color theme="0" tint="-0.14975432599871821"/>
       </right>
       <top/>
       <bottom style="thin">
-        <color theme="0" tint="-0.149784844508194"/>
+        <color theme="0" tint="-0.14975432599871821"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color theme="0" tint="-0.149754325998718"/>
+        <color theme="0" tint="-0.14972380748924222"/>
       </left>
       <right style="thin">
-        <color theme="0" tint="-0.149754325998718"/>
+        <color theme="0" tint="-0.14972380748924222"/>
       </right>
       <top style="thin">
-        <color theme="0" tint="-0.149754325998718"/>
+        <color theme="0" tint="-0.14972380748924222"/>
       </top>
       <bottom style="thin">
-        <color theme="0" tint="-0.149754325998718"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+        <color theme="0" tint="-0.14972380748924222"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,10 +984,10 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="22" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="23" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1530,58 +1027,33 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="3">
+    <cellStyle name="差" xfId="2" builtinId="27"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="好" xfId="1" builtinId="26"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="5">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1601,6 +1073,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1887,24 +1362,24 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="13.75" style="8" customWidth="1"/>
-    <col min="3" max="3" width="16.3833333333333" style="8" customWidth="1"/>
-    <col min="4" max="4" width="11.5" style="8" customWidth="1"/>
-    <col min="5" max="5" width="10.3833333333333" style="8" customWidth="1"/>
+    <col min="2" max="2" width="13.7265625" style="8" customWidth="1"/>
+    <col min="3" max="3" width="16.36328125" style="8" customWidth="1"/>
+    <col min="4" max="4" width="11.453125" style="8" customWidth="1"/>
+    <col min="5" max="5" width="10.36328125" style="8" customWidth="1"/>
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -1921,7 +1396,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="17" t="s">
         <v>5</v>
       </c>
@@ -1936,7 +1411,7 @@
       </c>
       <c r="E2" s="17"/>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="s">
         <v>7</v>
       </c>
@@ -1945,7 +1420,7 @@
       <c r="D3" s="17"/>
       <c r="E3" s="17"/>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
         <v>4</v>
       </c>
@@ -1962,7 +1437,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" s="21" customFormat="1" spans="1:6">
+    <row r="5" spans="1:6" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="22"/>
       <c r="B5" s="23">
         <v>1</v>
@@ -1977,7 +1452,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A6" s="24"/>
       <c r="B6" s="25">
         <v>1</v>
@@ -1993,7 +1468,7 @@
       </c>
       <c r="F6" s="26"/>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A7" s="24"/>
       <c r="B7" s="25">
         <v>1</v>
@@ -2009,7 +1484,7 @@
       </c>
       <c r="F7" s="26"/>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A8" s="24"/>
       <c r="B8" s="25">
         <v>1</v>
@@ -2025,7 +1500,7 @@
       </c>
       <c r="F8" s="26"/>
     </row>
-    <row r="9" customFormat="1" spans="1:6">
+    <row r="9" spans="1:6" customFormat="1" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A9" s="27"/>
       <c r="B9" s="25">
         <v>1</v>
@@ -2041,7 +1516,7 @@
       </c>
       <c r="F9" s="26"/>
     </row>
-    <row r="10" customFormat="1" spans="1:6">
+    <row r="10" spans="1:6" customFormat="1" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A10" s="27"/>
       <c r="B10" s="25">
         <v>1</v>
@@ -2057,7 +1532,7 @@
       </c>
       <c r="F10" s="26"/>
     </row>
-    <row r="11" s="21" customFormat="1" spans="1:6">
+    <row r="11" spans="1:6" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="22"/>
       <c r="B11" s="28">
         <v>2</v>
@@ -2072,7 +1547,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="24"/>
       <c r="B12" s="28">
         <v>2</v>
@@ -2088,7 +1563,7 @@
       </c>
       <c r="F12" s="11"/>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="24"/>
       <c r="B13" s="28">
         <v>2</v>
@@ -2104,7 +1579,7 @@
       </c>
       <c r="F13" s="11"/>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="24"/>
       <c r="B14" s="28">
         <v>2</v>
@@ -2120,7 +1595,7 @@
       </c>
       <c r="F14" s="11"/>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="24"/>
       <c r="B15" s="28">
         <v>2</v>
@@ -2136,7 +1611,7 @@
       </c>
       <c r="F15" s="11"/>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="24"/>
       <c r="B16" s="28">
         <v>2</v>
@@ -2153,33 +1628,32 @@
       <c r="F16" s="11"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="12" type="noConversion"/>
   <conditionalFormatting sqref="E4">
-    <cfRule type="cellIs" dxfId="0" priority="78" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="78" operator="equal">
       <formula>99999</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="13.75" style="8" customWidth="1"/>
-    <col min="3" max="3" width="16.3833333333333" style="8" customWidth="1"/>
-    <col min="4" max="4" width="11.5" style="8" customWidth="1"/>
-    <col min="5" max="5" width="17.3833333333333" style="8" customWidth="1"/>
+    <col min="2" max="2" width="13.7265625" style="8" customWidth="1"/>
+    <col min="3" max="3" width="16.36328125" style="8" customWidth="1"/>
+    <col min="4" max="4" width="11.453125" style="8" customWidth="1"/>
+    <col min="5" max="5" width="17.36328125" style="8" customWidth="1"/>
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -2196,7 +1670,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="17" t="s">
         <v>5</v>
       </c>
@@ -2211,7 +1685,7 @@
       </c>
       <c r="E2" s="17"/>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="s">
         <v>7</v>
       </c>
@@ -2220,7 +1694,7 @@
       <c r="D3" s="17"/>
       <c r="E3" s="17"/>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
         <v>4</v>
       </c>
@@ -2237,7 +1711,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B5" s="18">
         <v>1</v>
       </c>
@@ -2251,7 +1725,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B6" s="20">
         <v>2</v>
       </c>
@@ -2266,7 +1740,7 @@
       </c>
       <c r="F6" s="11"/>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B7" s="18">
         <v>1</v>
       </c>
@@ -2280,7 +1754,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B8" s="20">
         <v>2</v>
       </c>
@@ -2294,7 +1768,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B9" s="18">
         <v>1</v>
       </c>
@@ -2308,7 +1782,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B10" s="20">
         <v>2</v>
       </c>
@@ -2322,7 +1796,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B11" s="18">
         <v>1</v>
       </c>
@@ -2336,7 +1810,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B12" s="20">
         <v>2</v>
       </c>
@@ -2350,7 +1824,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B13" s="18">
         <v>1</v>
       </c>
@@ -2364,7 +1838,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B14" s="20">
         <v>2</v>
       </c>
@@ -2378,7 +1852,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B15" s="18">
         <v>1</v>
       </c>
@@ -2392,7 +1866,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B16" s="20">
         <v>2</v>
       </c>
@@ -2407,27 +1881,27 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="12" type="noConversion"/>
   <conditionalFormatting sqref="E4">
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
       <formula>99999</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor theme="1"/>
   </sheetPr>
   <dimension ref="A1:F67"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="16.5" spans="1:6">
+    <row r="1" spans="1:6" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>8</v>
       </c>
@@ -2444,7 +1918,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="16.5" spans="1:6">
+    <row r="2" spans="1:6" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -2459,7 +1933,7 @@
       </c>
       <c r="E2" s="8"/>
     </row>
-    <row r="3" s="1" customFormat="1" ht="16.5" spans="1:6">
+    <row r="3" spans="1:6" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A3" s="5">
         <v>1</v>
       </c>
@@ -2474,7 +1948,7 @@
       </c>
       <c r="E3" s="8"/>
     </row>
-    <row r="4" s="1" customFormat="1" ht="16.5" spans="1:6">
+    <row r="4" spans="1:6" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A4" s="5">
         <v>1</v>
       </c>
@@ -2489,7 +1963,7 @@
       </c>
       <c r="E4" s="8"/>
     </row>
-    <row r="5" s="1" customFormat="1" ht="16.5" spans="1:6">
+    <row r="5" spans="1:6" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A5" s="5">
         <v>1</v>
       </c>
@@ -2504,7 +1978,7 @@
       </c>
       <c r="E5" s="8"/>
     </row>
-    <row r="6" s="1" customFormat="1" ht="16.5" spans="1:6">
+    <row r="6" spans="1:6" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A6" s="5">
         <v>1</v>
       </c>
@@ -2519,7 +1993,7 @@
       </c>
       <c r="E6" s="8"/>
     </row>
-    <row r="7" s="1" customFormat="1" ht="16.5" spans="1:6">
+    <row r="7" spans="1:6" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A7" s="5">
         <v>1</v>
       </c>
@@ -2534,7 +2008,7 @@
       </c>
       <c r="E7" s="8"/>
     </row>
-    <row r="8" s="1" customFormat="1" ht="16.5" spans="1:6">
+    <row r="8" spans="1:6" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A8" s="5">
         <v>1</v>
       </c>
@@ -2550,7 +2024,7 @@
       <c r="E8" s="8"/>
       <c r="F8" s="11"/>
     </row>
-    <row r="9" s="1" customFormat="1" ht="16.5" spans="1:6">
+    <row r="9" spans="1:6" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A9" s="5">
         <v>1</v>
       </c>
@@ -2566,7 +2040,7 @@
       <c r="E9" s="8"/>
       <c r="F9" s="11"/>
     </row>
-    <row r="10" s="1" customFormat="1" ht="16.5" spans="1:6">
+    <row r="10" spans="1:6" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A10" s="5">
         <v>1</v>
       </c>
@@ -2582,7 +2056,7 @@
       <c r="E10" s="8"/>
       <c r="F10" s="11"/>
     </row>
-    <row r="11" s="1" customFormat="1" ht="16.5" spans="1:6">
+    <row r="11" spans="1:6" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A11" s="5">
         <v>1</v>
       </c>
@@ -2598,7 +2072,7 @@
       <c r="E11" s="8"/>
       <c r="F11" s="11"/>
     </row>
-    <row r="12" s="1" customFormat="1" ht="16.5" spans="1:6">
+    <row r="12" spans="1:6" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A12" s="5">
         <v>1</v>
       </c>
@@ -2614,7 +2088,7 @@
       <c r="E12" s="8"/>
       <c r="F12" s="11"/>
     </row>
-    <row r="13" s="1" customFormat="1" ht="16.5" spans="1:6">
+    <row r="13" spans="1:6" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A13" s="5">
         <v>1</v>
       </c>
@@ -2630,7 +2104,7 @@
       <c r="E13" s="8"/>
       <c r="F13" s="11"/>
     </row>
-    <row r="14" s="1" customFormat="1" ht="16.5" spans="1:6">
+    <row r="14" spans="1:6" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A14" s="5">
         <v>1</v>
       </c>
@@ -2646,7 +2120,7 @@
       <c r="E14" s="8"/>
       <c r="F14" s="11"/>
     </row>
-    <row r="15" s="1" customFormat="1" ht="16.5" spans="1:6">
+    <row r="15" spans="1:6" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A15" s="5">
         <v>1</v>
       </c>
@@ -2662,7 +2136,7 @@
       <c r="E15" s="8"/>
       <c r="F15" s="11"/>
     </row>
-    <row r="16" s="1" customFormat="1" ht="16.5" spans="1:6">
+    <row r="16" spans="1:6" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A16" s="5">
         <v>1</v>
       </c>
@@ -2678,7 +2152,7 @@
       <c r="E16" s="8"/>
       <c r="F16" s="11"/>
     </row>
-    <row r="17" s="1" customFormat="1" ht="16.5" spans="1:6">
+    <row r="17" spans="1:6" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A17" s="5">
         <v>1</v>
       </c>
@@ -2694,7 +2168,7 @@
       <c r="E17" s="8"/>
       <c r="F17" s="11"/>
     </row>
-    <row r="18" s="1" customFormat="1" ht="16.5" spans="1:6">
+    <row r="18" spans="1:6" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A18" s="5">
         <v>1</v>
       </c>
@@ -2710,7 +2184,7 @@
       <c r="E18" s="8"/>
       <c r="F18" s="11"/>
     </row>
-    <row r="19" s="1" customFormat="1" ht="16.5" spans="1:6">
+    <row r="19" spans="1:6" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A19" s="5">
         <v>1</v>
       </c>
@@ -2726,7 +2200,7 @@
       <c r="E19" s="8"/>
       <c r="F19" s="11"/>
     </row>
-    <row r="20" s="1" customFormat="1" ht="16.5" spans="1:6">
+    <row r="20" spans="1:6" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A20" s="5">
         <v>1</v>
       </c>
@@ -2742,7 +2216,7 @@
       <c r="E20" s="8"/>
       <c r="F20" s="11"/>
     </row>
-    <row r="21" s="1" customFormat="1" ht="16.5" spans="1:6">
+    <row r="21" spans="1:6" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A21" s="5">
         <v>1</v>
       </c>
@@ -2758,7 +2232,7 @@
       <c r="E21" s="8"/>
       <c r="F21" s="11"/>
     </row>
-    <row r="22" s="1" customFormat="1" ht="16.5" spans="1:6">
+    <row r="22" spans="1:6" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A22" s="5">
         <v>1</v>
       </c>
@@ -2776,7 +2250,7 @@
       <c r="E22" s="8"/>
       <c r="F22" s="11"/>
     </row>
-    <row r="23" s="1" customFormat="1" ht="16.5" spans="1:6">
+    <row r="23" spans="1:6" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A23" s="5">
         <v>1</v>
       </c>
@@ -2794,7 +2268,7 @@
       <c r="E23" s="8"/>
       <c r="F23" s="11"/>
     </row>
-    <row r="24" s="1" customFormat="1" ht="16.5" spans="1:6">
+    <row r="24" spans="1:6" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A24" s="5">
         <v>1</v>
       </c>
@@ -2812,7 +2286,7 @@
       <c r="E24" s="8"/>
       <c r="F24" s="11"/>
     </row>
-    <row r="25" s="1" customFormat="1" ht="16.5" spans="1:6">
+    <row r="25" spans="1:6" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A25" s="5">
         <v>1</v>
       </c>
@@ -2828,7 +2302,7 @@
       <c r="E25" s="8"/>
       <c r="F25" s="11"/>
     </row>
-    <row r="26" s="1" customFormat="1" ht="16.5" spans="1:6">
+    <row r="26" spans="1:6" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A26" s="5">
         <v>1</v>
       </c>
@@ -2844,7 +2318,7 @@
       <c r="E26" s="8"/>
       <c r="F26" s="11"/>
     </row>
-    <row r="27" s="1" customFormat="1" ht="16.5" spans="1:6">
+    <row r="27" spans="1:6" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A27" s="5">
         <v>1</v>
       </c>
@@ -2860,7 +2334,7 @@
       <c r="E27" s="8"/>
       <c r="F27" s="11"/>
     </row>
-    <row r="28" s="1" customFormat="1" ht="16.5" spans="1:6">
+    <row r="28" spans="1:6" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A28" s="5">
         <v>1</v>
       </c>
@@ -2876,7 +2350,7 @@
       <c r="E28" s="8"/>
       <c r="F28" s="11"/>
     </row>
-    <row r="29" s="1" customFormat="1" ht="16.5" spans="1:6">
+    <row r="29" spans="1:6" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A29" s="5">
         <v>1</v>
       </c>
@@ -2894,7 +2368,7 @@
       <c r="E29" s="8"/>
       <c r="F29" s="11"/>
     </row>
-    <row r="30" s="1" customFormat="1" ht="16.5" spans="1:6">
+    <row r="30" spans="1:6" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A30" s="5">
         <v>1</v>
       </c>
@@ -2912,7 +2386,7 @@
       <c r="E30" s="8"/>
       <c r="F30" s="11"/>
     </row>
-    <row r="31" s="1" customFormat="1" ht="16.5" spans="1:6">
+    <row r="31" spans="1:6" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A31" s="5">
         <v>1</v>
       </c>
@@ -2928,7 +2402,7 @@
       <c r="E31" s="8"/>
       <c r="F31" s="11"/>
     </row>
-    <row r="32" s="1" customFormat="1" ht="16.5" spans="1:6">
+    <row r="32" spans="1:6" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A32" s="5">
         <v>1</v>
       </c>
@@ -2944,7 +2418,7 @@
       <c r="E32" s="8"/>
       <c r="F32" s="11"/>
     </row>
-    <row r="33" s="1" customFormat="1" ht="16.5" spans="1:6">
+    <row r="33" spans="1:6" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A33" s="5">
         <v>1</v>
       </c>
@@ -2960,7 +2434,7 @@
       <c r="E33" s="8"/>
       <c r="F33" s="11"/>
     </row>
-    <row r="34" s="2" customFormat="1" ht="16.5" spans="1:6">
+    <row r="34" spans="1:6" s="2" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A34" s="5">
         <v>1</v>
       </c>
@@ -2978,7 +2452,7 @@
       <c r="E34" s="8"/>
       <c r="F34" s="11"/>
     </row>
-    <row r="35" s="1" customFormat="1" ht="16.5" spans="1:6">
+    <row r="35" spans="1:6" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A35" s="5">
         <v>2</v>
       </c>
@@ -2994,7 +2468,7 @@
       <c r="E35" s="8"/>
       <c r="F35" s="11"/>
     </row>
-    <row r="36" s="1" customFormat="1" ht="16.5" spans="1:6">
+    <row r="36" spans="1:6" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A36" s="5">
         <v>2</v>
       </c>
@@ -3010,7 +2484,7 @@
       <c r="E36" s="8"/>
       <c r="F36" s="11"/>
     </row>
-    <row r="37" s="1" customFormat="1" ht="16.5" spans="1:6">
+    <row r="37" spans="1:6" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A37" s="5">
         <v>2</v>
       </c>
@@ -3026,7 +2500,7 @@
       <c r="E37" s="8"/>
       <c r="F37" s="11"/>
     </row>
-    <row r="38" s="1" customFormat="1" ht="16.5" spans="1:6">
+    <row r="38" spans="1:6" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A38" s="5">
         <v>2</v>
       </c>
@@ -3042,7 +2516,7 @@
       <c r="E38" s="8"/>
       <c r="F38" s="11"/>
     </row>
-    <row r="39" s="1" customFormat="1" ht="16.5" spans="1:6">
+    <row r="39" spans="1:6" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A39" s="5">
         <v>2</v>
       </c>
@@ -3057,7 +2531,7 @@
       </c>
       <c r="E39" s="8"/>
     </row>
-    <row r="40" s="1" customFormat="1" ht="16.5" spans="1:6">
+    <row r="40" spans="1:6" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A40" s="5">
         <v>2</v>
       </c>
@@ -3072,7 +2546,7 @@
       </c>
       <c r="E40" s="8"/>
     </row>
-    <row r="41" s="1" customFormat="1" ht="16.5" spans="1:6">
+    <row r="41" spans="1:6" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A41" s="5">
         <v>2</v>
       </c>
@@ -3087,7 +2561,7 @@
       </c>
       <c r="E41" s="8"/>
     </row>
-    <row r="42" s="1" customFormat="1" ht="16.5" spans="1:6">
+    <row r="42" spans="1:6" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A42" s="5">
         <v>2</v>
       </c>
@@ -3102,7 +2576,7 @@
       </c>
       <c r="E42" s="8"/>
     </row>
-    <row r="43" s="1" customFormat="1" ht="16.5" spans="1:6">
+    <row r="43" spans="1:6" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A43" s="5">
         <v>2</v>
       </c>
@@ -3117,7 +2591,7 @@
       </c>
       <c r="E43" s="8"/>
     </row>
-    <row r="44" s="1" customFormat="1" ht="16.5" spans="1:6">
+    <row r="44" spans="1:6" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A44" s="5">
         <v>2</v>
       </c>
@@ -3132,7 +2606,7 @@
       </c>
       <c r="E44" s="8"/>
     </row>
-    <row r="45" s="1" customFormat="1" ht="16.5" spans="1:6">
+    <row r="45" spans="1:6" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A45" s="5">
         <v>2</v>
       </c>
@@ -3147,7 +2621,7 @@
       </c>
       <c r="E45" s="8"/>
     </row>
-    <row r="46" s="1" customFormat="1" ht="16.5" spans="1:6">
+    <row r="46" spans="1:6" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A46" s="5">
         <v>2</v>
       </c>
@@ -3162,7 +2636,7 @@
       </c>
       <c r="E46" s="8"/>
     </row>
-    <row r="47" s="1" customFormat="1" ht="16.5" spans="1:6">
+    <row r="47" spans="1:6" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A47" s="5">
         <v>2</v>
       </c>
@@ -3177,7 +2651,7 @@
       </c>
       <c r="E47" s="8"/>
     </row>
-    <row r="48" s="1" customFormat="1" ht="16.5" spans="1:6">
+    <row r="48" spans="1:6" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A48" s="5">
         <v>2</v>
       </c>
@@ -3192,7 +2666,7 @@
       </c>
       <c r="E48" s="8"/>
     </row>
-    <row r="49" s="1" customFormat="1" ht="16.5" spans="1:5">
+    <row r="49" spans="1:5" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A49" s="5">
         <v>2</v>
       </c>
@@ -3207,7 +2681,7 @@
       </c>
       <c r="E49" s="8"/>
     </row>
-    <row r="50" s="1" customFormat="1" ht="16.5" spans="1:5">
+    <row r="50" spans="1:5" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A50" s="5">
         <v>2</v>
       </c>
@@ -3222,7 +2696,7 @@
       </c>
       <c r="E50" s="8"/>
     </row>
-    <row r="51" s="1" customFormat="1" ht="16.5" spans="1:5">
+    <row r="51" spans="1:5" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A51" s="5">
         <v>2</v>
       </c>
@@ -3237,7 +2711,7 @@
       </c>
       <c r="E51" s="8"/>
     </row>
-    <row r="52" s="1" customFormat="1" ht="16.5" spans="1:5">
+    <row r="52" spans="1:5" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A52" s="5">
         <v>2</v>
       </c>
@@ -3252,7 +2726,7 @@
       </c>
       <c r="E52" s="8"/>
     </row>
-    <row r="53" s="1" customFormat="1" ht="16.5" spans="1:5">
+    <row r="53" spans="1:5" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A53" s="5">
         <v>2</v>
       </c>
@@ -3267,7 +2741,7 @@
       </c>
       <c r="E53" s="8"/>
     </row>
-    <row r="54" s="1" customFormat="1" ht="16.5" spans="1:5">
+    <row r="54" spans="1:5" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A54" s="5">
         <v>2</v>
       </c>
@@ -3282,7 +2756,7 @@
       </c>
       <c r="E54" s="8"/>
     </row>
-    <row r="55" s="1" customFormat="1" ht="16.5" spans="1:5">
+    <row r="55" spans="1:5" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A55" s="5">
         <v>2</v>
       </c>
@@ -3299,7 +2773,7 @@
       </c>
       <c r="E55" s="8"/>
     </row>
-    <row r="56" s="1" customFormat="1" ht="16.5" spans="1:5">
+    <row r="56" spans="1:5" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A56" s="5">
         <v>2</v>
       </c>
@@ -3316,7 +2790,7 @@
       </c>
       <c r="E56" s="8"/>
     </row>
-    <row r="57" s="1" customFormat="1" ht="16.5" spans="1:5">
+    <row r="57" spans="1:5" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A57" s="5">
         <v>2</v>
       </c>
@@ -3333,7 +2807,7 @@
       </c>
       <c r="E57" s="8"/>
     </row>
-    <row r="58" s="1" customFormat="1" ht="16.5" spans="1:5">
+    <row r="58" spans="1:5" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A58" s="5">
         <v>2</v>
       </c>
@@ -3348,7 +2822,7 @@
       </c>
       <c r="E58" s="8"/>
     </row>
-    <row r="59" s="1" customFormat="1" ht="16.5" spans="1:5">
+    <row r="59" spans="1:5" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A59" s="5">
         <v>2</v>
       </c>
@@ -3363,7 +2837,7 @@
       </c>
       <c r="E59" s="8"/>
     </row>
-    <row r="60" s="1" customFormat="1" ht="16.5" spans="1:5">
+    <row r="60" spans="1:5" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A60" s="5">
         <v>2</v>
       </c>
@@ -3378,7 +2852,7 @@
       </c>
       <c r="E60" s="8"/>
     </row>
-    <row r="61" s="1" customFormat="1" ht="16.5" spans="1:5">
+    <row r="61" spans="1:5" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A61" s="5">
         <v>2</v>
       </c>
@@ -3393,7 +2867,7 @@
       </c>
       <c r="E61" s="8"/>
     </row>
-    <row r="62" s="1" customFormat="1" ht="16.5" spans="1:5">
+    <row r="62" spans="1:5" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A62" s="5">
         <v>2</v>
       </c>
@@ -3410,7 +2884,7 @@
       </c>
       <c r="E62" s="8"/>
     </row>
-    <row r="63" s="1" customFormat="1" ht="16.5" spans="1:5">
+    <row r="63" spans="1:5" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A63" s="5">
         <v>2</v>
       </c>
@@ -3427,7 +2901,7 @@
       </c>
       <c r="E63" s="8"/>
     </row>
-    <row r="64" s="1" customFormat="1" ht="16.5" spans="1:5">
+    <row r="64" spans="1:5" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A64" s="5">
         <v>2</v>
       </c>
@@ -3442,7 +2916,7 @@
       </c>
       <c r="E64" s="8"/>
     </row>
-    <row r="65" s="1" customFormat="1" ht="16.5" spans="1:5">
+    <row r="65" spans="1:5" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A65" s="5">
         <v>2</v>
       </c>
@@ -3457,7 +2931,7 @@
       </c>
       <c r="E65" s="8"/>
     </row>
-    <row r="66" s="1" customFormat="1" ht="16.5" spans="1:5">
+    <row r="66" spans="1:5" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A66" s="5">
         <v>2</v>
       </c>
@@ -3472,7 +2946,7 @@
       </c>
       <c r="E66" s="8"/>
     </row>
-    <row r="67" s="1" customFormat="1" ht="16.5" spans="1:5">
+    <row r="67" spans="1:5" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.4">
       <c r="A67" s="15">
         <v>2</v>
       </c>
@@ -3490,21 +2964,21 @@
       <c r="E67" s="8"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="12" type="noConversion"/>
   <conditionalFormatting sqref="D1:E1">
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>99999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E22 E26:E67">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>99999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8:F9">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E22 E26:E67">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
-      <formula>99999</formula>
-    </cfRule>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>